--- a/SuppXLS/Scen_UC_DECEL_ELC_100.xlsx
+++ b/SuppXLS/Scen_UC_DECEL_ELC_100.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCB9E190-A545-4248-8A90-E1F03B048894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{826A63A9-B190-49F6-825A-A2D10D361280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{12993743-A3C9-4B22-8ADD-D2910F70577E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{12993743-A3C9-4B22-8ADD-D2910F70577E}"/>
   </bookViews>
   <sheets>
-    <sheet name="DECRHEAT_MANHEAT_10_15" sheetId="1" r:id="rId1"/>
+    <sheet name="DECELC_100" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -104,13 +104,13 @@
     <t>MANHEAT</t>
   </si>
   <si>
-    <t>DMD</t>
-  </si>
-  <si>
-    <t>DECRHEAT</t>
-  </si>
-  <si>
-    <t>UC_DECRHEAT_20_50</t>
+    <t>UC_DECELC_100</t>
+  </si>
+  <si>
+    <t>DECELC</t>
+  </si>
+  <si>
+    <t>ELC</t>
   </si>
 </sst>
 </file>
@@ -694,10 +694,10 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
         <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>22</v>
       </c>
       <c r="E6" t="s">
         <v>23</v>
@@ -732,10 +732,10 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
         <v>24</v>
-      </c>
-      <c r="C7" t="s">
-        <v>22</v>
       </c>
       <c r="E7" t="s">
         <v>23</v>

--- a/SuppXLS/Scen_UC_DECEL_ELC_100.xlsx
+++ b/SuppXLS/Scen_UC_DECEL_ELC_100.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{826A63A9-B190-49F6-825A-A2D10D361280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D0BA8D3-0B79-4671-9B82-D71027A57FAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{12993743-A3C9-4B22-8ADD-D2910F70577E}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{12993743-A3C9-4B22-8ADD-D2910F70577E}"/>
   </bookViews>
   <sheets>
     <sheet name="DECELC_100" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
   <si>
     <t>UC - Each Region/Period</t>
   </si>
@@ -96,12 +96,6 @@
   </si>
   <si>
     <t>Minimum Decenteralized  ELC penetration</t>
-  </si>
-  <si>
-    <t>UC_COMPRD</t>
-  </si>
-  <si>
-    <t>MANHEAT</t>
   </si>
   <si>
     <t>UC_DECELC_100</t>
@@ -694,19 +688,13 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" t="s">
         <v>22</v>
-      </c>
-      <c r="C6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" t="s">
-        <v>20</v>
       </c>
       <c r="I6">
         <v>2030</v>
@@ -718,7 +706,7 @@
         <v>1</v>
       </c>
       <c r="L6">
-        <v>-0.1</v>
+        <v>-1</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -732,19 +720,13 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" t="s">
         <v>22</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" t="s">
-        <v>21</v>
-      </c>
-      <c r="H7" t="s">
-        <v>20</v>
       </c>
       <c r="I7">
         <v>2050</v>
@@ -756,7 +738,7 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>-0.15</v>
+        <v>-1</v>
       </c>
       <c r="M7">
         <v>0</v>

--- a/SuppXLS/Scen_UC_DECEL_ELC_100.xlsx
+++ b/SuppXLS/Scen_UC_DECEL_ELC_100.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D0BA8D3-0B79-4671-9B82-D71027A57FAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B1F2A6B-C450-4186-8FCC-83F58D1EC73D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{12993743-A3C9-4B22-8ADD-D2910F70577E}"/>
   </bookViews>
   <sheets>
-    <sheet name="DECELC_100" sheetId="1" r:id="rId1"/>
+    <sheet name="DECELC_ELC_100" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>UC - Each Region/Period</t>
   </si>
@@ -98,13 +98,13 @@
     <t>Minimum Decenteralized  ELC penetration</t>
   </si>
   <si>
-    <t>UC_DECELC_100</t>
-  </si>
-  <si>
     <t>DECELC</t>
   </si>
   <si>
     <t>ELC</t>
+  </si>
+  <si>
+    <t>UC_DECELC_ELC_100</t>
   </si>
 </sst>
 </file>
@@ -608,7 +608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE217BF5-23EC-4D23-B173-E15767463FEB}">
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
@@ -688,13 +688,13 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
         <v>20</v>
       </c>
-      <c r="C6" t="s">
+      <c r="G6" t="s">
         <v>21</v>
-      </c>
-      <c r="G6" t="s">
-        <v>22</v>
       </c>
       <c r="I6">
         <v>2030</v>
@@ -715,38 +715,6 @@
         <v>15</v>
       </c>
       <c r="O6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G7" t="s">
-        <v>22</v>
-      </c>
-      <c r="I7">
-        <v>2050</v>
-      </c>
-      <c r="J7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>-1</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>15</v>
-      </c>
-      <c r="O7" t="s">
         <v>19</v>
       </c>
     </row>

--- a/SuppXLS/Scen_UC_DECEL_ELC_100.xlsx
+++ b/SuppXLS/Scen_UC_DECEL_ELC_100.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B1F2A6B-C450-4186-8FCC-83F58D1EC73D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C8481A0-BB08-48B9-9BAC-6D1D69975EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{12993743-A3C9-4B22-8ADD-D2910F70577E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
   <si>
     <t>UC - Each Region/Period</t>
   </si>
@@ -105,6 +105,9 @@
   </si>
   <si>
     <t>UC_DECELC_ELC_100</t>
+  </si>
+  <si>
+    <t>UC_COMPRD</t>
   </si>
 </sst>
 </file>
@@ -691,10 +694,16 @@
         <v>22</v>
       </c>
       <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" t="s">
         <v>20</v>
       </c>
       <c r="G6" t="s">
         <v>21</v>
+      </c>
+      <c r="H6" t="s">
+        <v>23</v>
       </c>
       <c r="I6">
         <v>2030</v>
